--- a/outputs/370-43.xlsx
+++ b/outputs/370-43.xlsx
@@ -1398,58 +1398,58 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2" t="s">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="9" t="e">
+      <c r="E18" s="2"/>
+      <c r="F18" s="9" t="n">
         <f aca="false">SUM(F19:F31)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G19" s="9" t="e">
+        <v>19</v>
+      </c>
+      <c r="G18" s="9" t="n">
         <f aca="false">SUM(G19:G31)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H19" s="9" t="e">
+        <v>3</v>
+      </c>
+      <c r="H18" s="9" t="n">
         <f aca="false">SUM(H19:H31)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I19" s="9" t="e">
+        <v>32</v>
+      </c>
+      <c r="I18" s="9" t="n">
         <f aca="false">SUM(I19:I31)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J19" s="9" t="e">
+        <v>66</v>
+      </c>
+      <c r="J18" s="9" t="n">
         <f aca="false">SUM(J19:J31)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K19" s="9" t="e">
+        <v>22</v>
+      </c>
+      <c r="K18" s="9" t="n">
         <f aca="false">SUM(K19:K31)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L19" s="9" t="e">
+        <v>38</v>
+      </c>
+      <c r="L18" s="9" t="n">
         <f aca="false">SUM(L19:L31)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M19" s="9" t="e">
+        <v>35</v>
+      </c>
+      <c r="M18" s="9" t="n">
         <f aca="false">SUM(M19:M31)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N19" s="9" t="e">
+        <v>22</v>
+      </c>
+      <c r="N18" s="9" t="n">
         <f aca="false">SUM(N19:N31)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O19" s="9"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
+        <v>237</v>
+      </c>
+      <c r="O18" s="9"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
@@ -1977,58 +1977,58 @@
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2" t="s">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="9" t="e">
+      <c r="E33" s="2"/>
+      <c r="F33" s="9" t="e">
         <f aca="false">SUM(F33:F42)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G34" s="9" t="e">
+      <c r="G33" s="9" t="e">
         <f aca="false">SUM(G33:G42)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H34" s="9" t="e">
+      <c r="H33" s="9" t="e">
         <f aca="false">SUM(H33:H42)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I34" s="9" t="e">
+      <c r="I33" s="9" t="e">
         <f aca="false">SUM(I33:I42)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J34" s="9" t="e">
+      <c r="J33" s="9" t="e">
         <f aca="false">SUM(J33:J42)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K34" s="9" t="e">
+      <c r="K33" s="9" t="e">
         <f aca="false">SUM(K33:K42)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L34" s="9" t="e">
+      <c r="L33" s="9" t="e">
         <f aca="false">SUM(L33:L42)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M34" s="9" t="e">
+      <c r="M33" s="9" t="e">
         <f aca="false">SUM(M33:M42)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N34" s="9" t="e">
+      <c r="N33" s="9" t="e">
         <f aca="false">SUM(N33:N42)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O34" s="9"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
@@ -2440,58 +2440,58 @@
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2" t="s">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="9" t="e">
+      <c r="E45" s="2"/>
+      <c r="F45" s="9" t="e">
         <f aca="false">SUM(F44:F54)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G46" s="9" t="e">
+      <c r="G45" s="9" t="e">
         <f aca="false">SUM(G44:G54)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H46" s="9" t="e">
+      <c r="H45" s="9" t="e">
         <f aca="false">SUM(H44:H54)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I46" s="9" t="e">
+      <c r="I45" s="9" t="e">
         <f aca="false">SUM(I44:I54)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J46" s="9" t="e">
+      <c r="J45" s="9" t="e">
         <f aca="false">SUM(J44:J54)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K46" s="9" t="e">
+      <c r="K45" s="9" t="e">
         <f aca="false">SUM(K44:K54)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L46" s="9" t="e">
+      <c r="L45" s="9" t="e">
         <f aca="false">SUM(L44:L54)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M46" s="9" t="e">
+      <c r="M45" s="9" t="e">
         <f aca="false">SUM(M44:M54)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N46" s="9" t="e">
+      <c r="N45" s="9" t="e">
         <f aca="false">SUM(N44:N54)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O46" s="9"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3"/>
-      <c r="S46" s="3"/>
-      <c r="T46" s="3"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
